--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itsve\Desktop\Hack Club 2026\blueprint\blueprint_projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itsve\Desktop\Hack Club 2026\git-blueprint\Splitix-MK1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73704A86-C4CA-4936-AFCB-D6388DD79F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D808B4A-F4C1-41C4-9EE6-6859E03A63CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{D7131E9E-EFEB-4C66-A522-603917819AB5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
   <si>
     <t>Product</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>5 left + 5 right</t>
+  </si>
+  <si>
+    <t>OR</t>
   </si>
 </sst>
 </file>
@@ -217,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -250,6 +253,21 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -620,499 +638,524 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="15">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="10">
+      <c r="C2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="14">
         <v>758</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="16">
         <f>B2*D2</f>
         <v>1516</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="12"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="12"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="12"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B7" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="C7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="10">
         <v>55</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3">
-        <f t="shared" ref="F3:F19" si="0">B3*D3</f>
+      <c r="E7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" ref="F7:F23" si="0">B7*D7</f>
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B8" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="10">
+      <c r="C8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="10">
         <v>29</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="3">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B9" s="8">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="10">
         <v>156</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3">
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="10">
         <v>91</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="3">
-        <f>6*D6</f>
+      <c r="E10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="3">
+        <f>6*D10</f>
         <v>546</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B11" s="8">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3">
         <f t="shared" si="0"/>
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B12" s="8">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="10">
         <v>0.62</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E12" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3">
         <f t="shared" si="0"/>
         <v>1.24</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B13" s="8">
         <v>2</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D13" s="10">
         <v>99</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E13" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3">
         <f t="shared" si="0"/>
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="8">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="B14" s="8">
+        <v>6</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="10">
         <v>45</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E14" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="3">
         <f t="shared" si="0"/>
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B15" s="8">
         <v>95</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="10">
+      <c r="C15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="10">
         <v>1.53</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="E15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3">
         <f t="shared" si="0"/>
         <v>145.35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1199</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="3">
-        <f>2*D12</f>
-        <v>2398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1299</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="6">
-        <f>D13</f>
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="8">
-        <v>75</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="10">
-        <v>10</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="3">
-        <f>B14*D14</f>
-        <v>750</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="10">
-        <v>15</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="3">
-        <f>8*D15</f>
-        <v>120</v>
-      </c>
-    </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="11">
+        <v>1199</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3">
+        <f>2*D16</f>
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1299</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="6">
+        <f>D17</f>
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="8">
+        <v>75</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="10">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3">
+        <f>B18*D18</f>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="10">
+        <v>15</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="3">
+        <f>8*D19</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B20" s="8">
         <v>2</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="10">
+      <c r="C20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="10">
         <v>251</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="3">
+      <c r="E20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="3">
         <f t="shared" si="0"/>
         <v>502</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B21" s="8">
         <v>2</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="C21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="10">
         <v>1.42</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="E21" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3">
         <f t="shared" si="0"/>
         <v>2.84</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B22" s="8">
         <v>2</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="10">
+      <c r="C22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="10">
         <v>14</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="E22" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="2" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B23" s="8">
         <v>2</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="10">
+      <c r="C23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="10">
         <v>3</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="E23" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B24" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="10">
+      <c r="C24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="10">
         <v>5000</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" s="3">
-        <f>D20</f>
+      <c r="E24" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="3">
+        <f>D24</f>
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B25" s="8">
         <v>1</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="10">
+      <c r="C25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="10">
         <v>530</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" s="10">
-        <f>D21</f>
+      <c r="E25" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="10">
+        <f>D25</f>
         <v>530</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B26" s="8">
         <v>1</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23">
-        <f>SUM(F2:F21)</f>
-        <v>13793.59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="E27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27">
+        <f>SUM(F2:F25)</f>
+        <v>13793.59</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="F2:F6"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://robu.in/product/promicro-nrf52840-development-board/" xr:uid="{8340C7B4-9557-4E84-BF93-A84178D9DB35}"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://robu.in/product/hongyan-ec11h-7ce20p1zd20-rotary-encoder-with-push-button-switch-vertical-plug-in-5-pin/" xr:uid="{0E45EC16-1A9C-471B-A90F-DA14CB828926}"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://robu.in/product/potentiometer-knob-rotary-switch-cap-black-color-pack-of-5-pcs/" xr:uid="{C6C61AF3-5C8D-49CE-8B2B-7D8D20FFE227}"/>
-    <hyperlink ref="E5" r:id="rId4" display="https://robu.in/product/0-96-inch-yellow-yellow-blue-oled-lcd-led-display-module/" xr:uid="{98026234-B7A3-4891-933C-8D945B8C667A}"/>
-    <hyperlink ref="E6" r:id="rId5" display="https://robu.in/product/16bit-ws2812b-5050-rgb-led-built-in-full-color-driving-lights-circular-development-board/" xr:uid="{AB45F1EB-B482-4476-A4F7-0A3785057ED8}"/>
-    <hyperlink ref="E7" r:id="rId6" display="https://robu.in/product/330-ohm-0-25w-metal-film-resistor-pack-of-100/" xr:uid="{13750CCC-9A96-48DB-8C13-D18655AA6C20}"/>
-    <hyperlink ref="E8" r:id="rId7" display="https://robu.in/product/mcmf0w4ff8203a50-multicomp-pro-metal-film-resistor-820kohm-250mw-1/" xr:uid="{533A4FDF-AE5E-4CDA-8EDD-DA2338C61FBF}"/>
-    <hyperlink ref="E9" r:id="rId8" display="https://www.amazon.in/Electronic-Spices-Tolerance-Through-Resistors/dp/B0BDDRD9DN" xr:uid="{9A9DBADD-BB5D-4582-BC0C-C8A6E83188B1}"/>
-    <hyperlink ref="E10" r:id="rId9" display="https://robu.in/product/cl21a107mqynnwe-samsang-6-3v-100uf-x5r-%C2%B120-0805-multilayer-ceramic-capacitors-mlcc-smd-smt-rohs/" xr:uid="{E4D35611-5152-4BE8-BEB5-58E9699A55D6}"/>
-    <hyperlink ref="E11" r:id="rId10" display="https://robu.in/product/cc0805jrx7r9bb104-yageo-smd-multilayer-ceramic-capacitor-0-1-%C2%B5f-50-v-0805-2012-metric-%C2%B1-5-x7r-cc-series/" xr:uid="{452C37F8-B50A-42F2-8F51-BE9B5070995D}"/>
-    <hyperlink ref="E12" r:id="rId11" display="https://stackskb.com/store/akko-creamy-cyan-switch-pack-of-45-pre-order/" xr:uid="{B8BAA340-95E2-4BAB-BABD-DA077BAF83A5}"/>
-    <hyperlink ref="E13" r:id="rId12" display="https://stackskb.com/store/veekos-gradient-keycaps-cherry-profile-135-keys/" xr:uid="{BA776530-2D82-4845-B663-AFAA1DD7048B}"/>
-    <hyperlink ref="E14" r:id="rId13" display="https://stackskb.com/store/ttc-pokayoke-hotswap-sockets-v2-10000-cycles/" xr:uid="{E395F011-2987-494A-80C2-CB5E74B15595}"/>
-    <hyperlink ref="E15" r:id="rId14" display="https://stackskb.com/store/1n4148-through-hole-diode/" xr:uid="{1752D0CB-27AD-43D6-BFD7-A3432AC57699}"/>
-    <hyperlink ref="E16" r:id="rId15" display="https://robu.in/product/nova-803450-1500mah-3-7v-lipo-battery-pack/" xr:uid="{3A0A80FB-3DD9-458F-8541-C5E6520F4901}"/>
-    <hyperlink ref="E17" r:id="rId16" display="https://robu.in/product/jst-sh-2-pin-connector-2mm-pitch/" xr:uid="{CB2B6FD8-6C2F-4BDE-A051-C83532EB4549}"/>
-    <hyperlink ref="E18" r:id="rId17" display="https://robu.in/product/tp4056-1a-li-ion-lithium-battery-charging-module-with-current-protection-type-c/" xr:uid="{B25A1E9B-BAA5-400E-A6AD-BB9C6D027242}"/>
-    <hyperlink ref="E19" r:id="rId18" display="https://robu.in/product/slide-switch-ss-12d03-1p2t/" xr:uid="{F42FA888-0D23-4757-8D57-9E7C24DED2BF}"/>
-    <hyperlink ref="E20" r:id="rId19" display="https://robu.in/product/online-pcb-manufacturing-service/" xr:uid="{1B715CF9-8C16-4E9A-BA47-112707B7FB4E}"/>
-    <hyperlink ref="E21" r:id="rId20" display="https://robu.in/product/3d-printing-service/" xr:uid="{13E33F18-B36B-454C-BF36-1569E1A312DC}"/>
+    <hyperlink ref="E11" r:id="rId1" display="https://robu.in/product/330-ohm-0-25w-metal-film-resistor-pack-of-100/" xr:uid="{13750CCC-9A96-48DB-8C13-D18655AA6C20}"/>
+    <hyperlink ref="E12" r:id="rId2" display="https://robu.in/product/mcmf0w4ff8203a50-multicomp-pro-metal-film-resistor-820kohm-250mw-1/" xr:uid="{533A4FDF-AE5E-4CDA-8EDD-DA2338C61FBF}"/>
+    <hyperlink ref="E13" r:id="rId3" display="https://www.amazon.in/Electronic-Spices-Tolerance-Through-Resistors/dp/B0BDDRD9DN" xr:uid="{9A9DBADD-BB5D-4582-BC0C-C8A6E83188B1}"/>
+    <hyperlink ref="E14" r:id="rId4" display="https://robu.in/product/cl21a107mqynnwe-samsang-6-3v-100uf-x5r-%C2%B120-0805-multilayer-ceramic-capacitors-mlcc-smd-smt-rohs/" xr:uid="{E4D35611-5152-4BE8-BEB5-58E9699A55D6}"/>
+    <hyperlink ref="E15" r:id="rId5" display="https://robu.in/product/cc0805jrx7r9bb104-yageo-smd-multilayer-ceramic-capacitor-0-1-%C2%B5f-50-v-0805-2012-metric-%C2%B1-5-x7r-cc-series/" xr:uid="{452C37F8-B50A-42F2-8F51-BE9B5070995D}"/>
+    <hyperlink ref="E16" r:id="rId6" display="https://stackskb.com/store/akko-creamy-cyan-switch-pack-of-45-pre-order/" xr:uid="{B8BAA340-95E2-4BAB-BABD-DA077BAF83A5}"/>
+    <hyperlink ref="E17" r:id="rId7" display="https://stackskb.com/store/veekos-gradient-keycaps-cherry-profile-135-keys/" xr:uid="{BA776530-2D82-4845-B663-AFAA1DD7048B}"/>
+    <hyperlink ref="E18" r:id="rId8" display="https://stackskb.com/store/ttc-pokayoke-hotswap-sockets-v2-10000-cycles/" xr:uid="{E395F011-2987-494A-80C2-CB5E74B15595}"/>
+    <hyperlink ref="E19" r:id="rId9" display="https://stackskb.com/store/1n4148-through-hole-diode/" xr:uid="{1752D0CB-27AD-43D6-BFD7-A3432AC57699}"/>
+    <hyperlink ref="E20" r:id="rId10" display="https://robu.in/product/nova-803450-1500mah-3-7v-lipo-battery-pack/" xr:uid="{3A0A80FB-3DD9-458F-8541-C5E6520F4901}"/>
+    <hyperlink ref="E21" r:id="rId11" display="https://robu.in/product/jst-sh-2-pin-connector-2mm-pitch/" xr:uid="{CB2B6FD8-6C2F-4BDE-A051-C83532EB4549}"/>
+    <hyperlink ref="E22" r:id="rId12" display="https://robu.in/product/tp4056-1a-li-ion-lithium-battery-charging-module-with-current-protection-type-c/" xr:uid="{B25A1E9B-BAA5-400E-A6AD-BB9C6D027242}"/>
+    <hyperlink ref="E23" r:id="rId13" display="https://robu.in/product/slide-switch-ss-12d03-1p2t/" xr:uid="{F42FA888-0D23-4757-8D57-9E7C24DED2BF}"/>
+    <hyperlink ref="E24" r:id="rId14" display="https://robu.in/product/online-pcb-manufacturing-service/" xr:uid="{1B715CF9-8C16-4E9A-BA47-112707B7FB4E}"/>
+    <hyperlink ref="E25" r:id="rId15" display="https://robu.in/product/3d-printing-service/" xr:uid="{13E33F18-B36B-454C-BF36-1569E1A312DC}"/>
+    <hyperlink ref="E7" r:id="rId16" display="https://robu.in/product/hongyan-ec11h-7ce20p1zd20-rotary-encoder-with-push-button-switch-vertical-plug-in-5-pin/" xr:uid="{0E45EC16-1A9C-471B-A90F-DA14CB828926}"/>
+    <hyperlink ref="E8" r:id="rId17" display="https://robu.in/product/potentiometer-knob-rotary-switch-cap-black-color-pack-of-5-pcs/" xr:uid="{C6C61AF3-5C8D-49CE-8B2B-7D8D20FFE227}"/>
+    <hyperlink ref="E9" r:id="rId18" display="https://robu.in/product/0-96-inch-yellow-yellow-blue-oled-lcd-led-display-module/" xr:uid="{98026234-B7A3-4891-933C-8D945B8C667A}"/>
+    <hyperlink ref="E10" r:id="rId19" display="https://robu.in/product/16bit-ws2812b-5050-rgb-led-built-in-full-color-driving-lights-circular-development-board/" xr:uid="{AB45F1EB-B482-4476-A4F7-0A3785057ED8}"/>
+    <hyperlink ref="E2" r:id="rId20" display="https://robu.in/product/promicro-nrf52840-development-board/" xr:uid="{FE2E5A48-6C22-4CB9-BCF4-89DB39B1A0C9}"/>
+    <hyperlink ref="E4" r:id="rId21" display="https://robu.in/product/pro-micro-nrf52840-development-board-compatible-with-nicenano-v2-0/" xr:uid="{F439CF93-CCAE-451D-8485-C134405E450E}"/>
+    <hyperlink ref="E6" r:id="rId22" display="https://probots.co.in/pro-micro-nrf52840-development-board-compatible-with-nice-nano-v2-0.html" xr:uid="{A687CE3E-A85D-4A83-A25C-6797F6ABEF8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
 </worksheet>
 </file>